--- a/HorseLuis/VTT Tool/VTT DATA.xlsx
+++ b/HorseLuis/VTT Tool/VTT DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Porjects\HorseLuis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A8DC1B-8091-4A13-BCC6-0B53C38D4736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D52AA2-6959-4231-AF58-80B60A956621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
   <sheets>
     <sheet name="VTT actif" sheetId="1" r:id="rId1"/>
@@ -754,7 +754,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="181">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -1294,6 +1294,9 @@
   </si>
   <si>
     <t>TRYAR</t>
+  </si>
+  <si>
+    <t>Horse Argentina</t>
   </si>
 </sst>
 </file>
@@ -2029,13 +2032,13 @@
     <col min="3" max="3" width="9.28515625" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.42578125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="13.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="12.5703125" style="9" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="15.42578125" style="9" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.42578125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="15.42578125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="9" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="15.42578125" style="9" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="34" width="10.42578125" customWidth="1"/>
@@ -2378,7 +2381,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="3" spans="1:58" hidden="1">
+    <row r="3" spans="1:58">
       <c r="A3" s="5" t="s">
         <v>171</v>
       </c>
@@ -2541,7 +2544,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="4" spans="1:58" hidden="1">
+    <row r="4" spans="1:58">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -2716,7 +2719,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="5" spans="1:58" hidden="1">
+    <row r="5" spans="1:58">
       <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="6" spans="1:58" hidden="1">
+    <row r="6" spans="1:58">
       <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
@@ -3061,7 +3064,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="7" spans="1:58" hidden="1">
+    <row r="7" spans="1:58">
       <c r="A7" s="5" t="s">
         <v>146</v>
       </c>
@@ -3236,7 +3239,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="8" spans="1:58" hidden="1">
+    <row r="8" spans="1:58">
       <c r="A8" s="5" t="s">
         <v>147</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="9" spans="1:58" hidden="1">
+    <row r="9" spans="1:58">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>90016000</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -3582,7 +3585,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="10" spans="1:58" hidden="1">
+    <row r="10" spans="1:58">
       <c r="A10" s="5" t="s">
         <v>168</v>
       </c>
@@ -3744,7 +3747,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="11" spans="1:58" hidden="1">
+    <row r="11" spans="1:58">
       <c r="A11" s="5" t="s">
         <v>172</v>
       </c>
@@ -11520,9 +11523,9 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <autoFilter ref="A1:AY55" xr:uid="{869D9611-F0E3-4A7A-9239-9C1FA0F0C8DA}">
-    <filterColumn colId="1">
+    <filterColumn colId="47">
       <filters>
-        <filter val="PORTUGAL"/>
+        <filter val="Direct"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/HorseLuis/VTT Tool/VTT DATA.xlsx
+++ b/HorseLuis/VTT Tool/VTT DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLMEDOGALVEZJorgeLui\Python Porjects\HorseLuis\VTT Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D52AA2-6959-4231-AF58-80B60A956621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364E7D07-101A-4478-91B4-7969C0CBC0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7F9BAF1D-C4F9-4C63-99BA-ADCB8DC6383A}"/>
   </bookViews>
@@ -754,7 +754,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="182">
   <si>
     <t>Compte Consignee</t>
   </si>
@@ -1297,6 +1297,9 @@
   </si>
   <si>
     <t>Horse Argentina</t>
+  </si>
+  <si>
+    <t>O0012</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1529,12 +1532,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1685,6 +1699,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8054,7 +8072,7 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="36" spans="1:51" hidden="1">
+    <row r="36" spans="1:51" ht="30" hidden="1">
       <c r="A36" s="5">
         <v>931</v>
       </c>
@@ -11497,6 +11515,11 @@
       </c>
       <c r="AY55" s="40">
         <v>46507</v>
+      </c>
+    </row>
+    <row r="56" spans="1:51">
+      <c r="A56" s="51" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:51">
